--- a/sample_data.xlsx
+++ b/sample_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,6 +434,11 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>No of weeks</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>status</t>
         </is>
       </c>
@@ -454,7 +459,10 @@
           <t>arjun@example.com</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>done</t>
         </is>
@@ -476,7 +484,10 @@
           <t>meera@example.com</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>partially paid</t>
         </is>
@@ -498,7 +509,10 @@
           <t>rahul@example.com</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>done</t>
         </is>
@@ -520,7 +534,10 @@
           <t>sneha@example.com</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t>partially paid</t>
         </is>
@@ -542,7 +559,10 @@
           <t>kiran@example.com</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>done</t>
         </is>
